--- a/backend/银行流水总表_脱敏版.xlsx
+++ b/backend/银行流水总表_脱敏版.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -444,6 +444,9 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -514,10 +517,25 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>来源文件名</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>来源相对路径</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>处理时间</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>节假日名称</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>非工作日标签</t>
         </is>
@@ -526,7 +544,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20260615094310775915e3db26c3f2d04ecd90dd544187d07c35</t>
+          <t>20260615095122425442a1ab4bbf392143c5bd1ca8a50c70faa9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -570,7 +588,7 @@
           <t>BJ20240105001</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>工作日</t>
         </is>
@@ -579,7 +597,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>20260615094310776032059255e9c6d540cd90b2e5303a34903d</t>
+          <t>20260615095122425701b7148cf2e35240c1be0aa4b7ff5aea7b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -623,7 +641,7 @@
           <t>BJ20240110002</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>工作日</t>
         </is>
